--- a/filer_2/89866618_boconcept_a_s.xlsx
+++ b/filer_2/89866618_boconcept_a_s.xlsx
@@ -6667,20 +6667,20 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>SUM(B5:B8)</f>
+        <f>IF(COUNT('res_raw_89866618'!$F$2,'res_raw_89866618'!$F$3,'res_raw_89866618'!$F$4,'res_raw_89866618'!$F$5)=0,'res_raw_89866618'!$F$6,SUM(B5:B8))</f>
         <v/>
       </c>
       <c r="C9" s="27">
-        <f>SUM(C5:C8)</f>
+        <f>IF(COUNT('res_raw_89866618'!$E$2,'res_raw_89866618'!$E$3,'res_raw_89866618'!$E$4,'res_raw_89866618'!$E$5)=0,'res_raw_89866618'!$E$6,SUM(C5:C8))</f>
         <v/>
       </c>
       <c r="D9" s="27">
-        <f>SUM(D5:D8)</f>
+        <f>IF(COUNT('res_raw_89866618'!$D$2,'res_raw_89866618'!$D$3,'res_raw_89866618'!$D$4,'res_raw_89866618'!$D$5)=0,'res_raw_89866618'!$D$6,SUM(D5:D8))</f>
         <v/>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>Beregnet: Nettoomsætning + Andre driftsindt. − Vareforbrug − Andre ext. omk.</t>
+          <t>Beregnet: Nettoomsætning + Andre driftsindt. − Vareforbrug − Andre ext. omk. Er komponenterne ikke indberettet, vises rapporteret bruttoresultat (fsa:GrossResult) direkte.</t>
         </is>
       </c>
     </row>

--- a/filer_2/89866618_boconcept_a_s.xlsx
+++ b/filer_2/89866618_boconcept_a_s.xlsx
@@ -6667,15 +6667,15 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>IF(COUNT('res_raw_89866618'!$F$2,'res_raw_89866618'!$F$3,'res_raw_89866618'!$F$4,'res_raw_89866618'!$F$5)=0,'res_raw_89866618'!$F$6,SUM(B5:B8))</f>
+        <f>IF(ABS((SUM(B5:B8))-'res_raw_89866618'!$F$6)&lt;=2,SUM(B5:B8),'res_raw_89866618'!$F$6)</f>
         <v/>
       </c>
       <c r="C9" s="27">
-        <f>IF(COUNT('res_raw_89866618'!$E$2,'res_raw_89866618'!$E$3,'res_raw_89866618'!$E$4,'res_raw_89866618'!$E$5)=0,'res_raw_89866618'!$E$6,SUM(C5:C8))</f>
+        <f>IF(ABS((SUM(C5:C8))-'res_raw_89866618'!$E$6)&lt;=2,SUM(C5:C8),'res_raw_89866618'!$E$6)</f>
         <v/>
       </c>
       <c r="D9" s="27">
-        <f>IF(COUNT('res_raw_89866618'!$D$2,'res_raw_89866618'!$D$3,'res_raw_89866618'!$D$4,'res_raw_89866618'!$D$5)=0,'res_raw_89866618'!$D$6,SUM(D5:D8))</f>
+        <f>IF(ABS((SUM(D5:D8))-'res_raw_89866618'!$D$6)&lt;=2,SUM(D5:D8),'res_raw_89866618'!$D$6)</f>
         <v/>
       </c>
       <c r="F9" s="28" t="inlineStr">
@@ -6763,15 +6763,15 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(B9:B12)</f>
+        <f>IF(ABS((SUM(B9:B12))-'res_raw_89866618'!$F$11)&lt;=2,SUM(B9:B12),'res_raw_89866618'!$F$11)</f>
         <v/>
       </c>
       <c r="C13" s="27">
-        <f>SUM(C9:C12)</f>
+        <f>IF(ABS((SUM(C9:C12))-'res_raw_89866618'!$E$11)&lt;=2,SUM(C9:C12),'res_raw_89866618'!$E$11)</f>
         <v/>
       </c>
       <c r="D13" s="27">
-        <f>SUM(D9:D12)</f>
+        <f>IF(ABS((SUM(D9:D12))-'res_raw_89866618'!$D$11)&lt;=2,SUM(D9:D12),'res_raw_89866618'!$D$11)</f>
         <v/>
       </c>
       <c r="F13" s="28" t="inlineStr">
@@ -6835,15 +6835,15 @@
         </is>
       </c>
       <c r="B16" s="27">
-        <f>SUM(B13:B15)</f>
+        <f>IF(ABS((SUM(B13:B15))-'res_raw_89866618'!$F$16)&lt;=2,SUM(B13:B15),'res_raw_89866618'!$F$16)</f>
         <v/>
       </c>
       <c r="C16" s="27">
-        <f>SUM(C13:C15)</f>
+        <f>IF(ABS((SUM(C13:C15))-'res_raw_89866618'!$E$16)&lt;=2,SUM(C13:C15),'res_raw_89866618'!$E$16)</f>
         <v/>
       </c>
       <c r="D16" s="27">
-        <f>SUM(D13:D15)</f>
+        <f>IF(ABS((SUM(D13:D15))-'res_raw_89866618'!$D$16)&lt;=2,SUM(D13:D15),'res_raw_89866618'!$D$16)</f>
         <v/>
       </c>
       <c r="F16" s="28" t="inlineStr">
@@ -7737,7 +7737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8013,27 +8013,21 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:SalesAndMarketingExpense</t>
+          <t>ifrs-full:TradeAndOtherCurrentReceivablesDueFromRelatedParties</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:SalesAndMarketingExpense</t>
-        </is>
-      </c>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n">
-        <v>50493</v>
-      </c>
-      <c r="F9" s="35" t="n">
-        <v>49838</v>
-      </c>
-      <c r="G9" s="35" t="n">
-        <v>39200</v>
-      </c>
-      <c r="H9" s="35" t="n">
-        <v>20029</v>
-      </c>
+          <t>ifrs-full:TradeAndOtherCurrentReceivablesDueFromRelatedParties</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="n">
+        <v>17320</v>
+      </c>
+      <c r="E9" s="35" t="n"/>
+      <c r="F9" s="35" t="n"/>
+      <c r="G9" s="35" t="n"/>
+      <c r="H9" s="35" t="n"/>
       <c r="I9" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8048,57 +8042,28 @@
       </c>
       <c r="B10" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:TradeAndOtherCurrentReceivablesDueFromRelatedParties</t>
+          <t>ifrs-full:TransportationExpense</t>
         </is>
       </c>
       <c r="C10" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:TradeAndOtherCurrentReceivablesDueFromRelatedParties</t>
-        </is>
-      </c>
-      <c r="D10" s="38" t="n">
-        <v>17320</v>
-      </c>
-      <c r="E10" s="38" t="n"/>
-      <c r="F10" s="38" t="n"/>
-      <c r="G10" s="38" t="n"/>
-      <c r="H10" s="38" t="n"/>
+          <t>ifrs-full:TransportationExpense</t>
+        </is>
+      </c>
+      <c r="D10" s="38" t="n"/>
+      <c r="E10" s="38" t="n">
+        <v>92067</v>
+      </c>
+      <c r="F10" s="38" t="n">
+        <v>54499</v>
+      </c>
+      <c r="G10" s="38" t="n">
+        <v>50352</v>
+      </c>
+      <c r="H10" s="38" t="n">
+        <v>45468</v>
+      </c>
       <c r="I10" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:TransportationExpense</t>
-        </is>
-      </c>
-      <c r="C11" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:TransportationExpense</t>
-        </is>
-      </c>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n">
-        <v>92067</v>
-      </c>
-      <c r="F11" s="35" t="n">
-        <v>54499</v>
-      </c>
-      <c r="G11" s="35" t="n">
-        <v>50352</v>
-      </c>
-      <c r="H11" s="35" t="n">
-        <v>45468</v>
-      </c>
-      <c r="I11" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer_2/89866618_boconcept_a_s.xlsx
+++ b/filer_2/89866618_boconcept_a_s.xlsx
@@ -5074,9 +5074,15 @@
       </c>
       <c r="B6" s="17" t="n"/>
       <c r="C6" s="17" t="n"/>
-      <c r="D6" s="17" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="F6" s="17" t="n"/>
+      <c r="D6" s="17" t="n">
+        <v>521010</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>454055</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>451361</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -5225,11 +5231,21 @@
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
-      <c r="F15" s="17" t="n"/>
+      <c r="B15" s="17" t="n">
+        <v>963</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>-6014</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>2293</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>-3075</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
